--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1417"/>
+  <dimension ref="A1:G1535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38101,7 +38101,7 @@
     </row>
     <row r="1300">
       <c r="A1300" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
     </row>
     <row r="1301">
       <c r="A1301" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
     </row>
     <row r="1303">
       <c r="A1303" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
     </row>
     <row r="1304">
       <c r="A1304" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
     </row>
     <row r="1305">
       <c r="A1305" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
     </row>
     <row r="1306">
       <c r="A1306" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
     </row>
     <row r="1307">
       <c r="A1307" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
     </row>
     <row r="1308">
       <c r="A1308" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
     </row>
     <row r="1309">
       <c r="A1309" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
     </row>
     <row r="1310">
       <c r="A1310" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
     </row>
     <row r="1311">
       <c r="A1311" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
     </row>
     <row r="1312">
       <c r="A1312" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
     </row>
     <row r="1313">
       <c r="A1313" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
     </row>
     <row r="1314">
       <c r="A1314" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
     </row>
     <row r="1315">
       <c r="A1315" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
     </row>
     <row r="1316">
       <c r="A1316" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
     </row>
     <row r="1317">
       <c r="A1317" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
     </row>
     <row r="1318">
       <c r="A1318" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
     </row>
     <row r="1319">
       <c r="A1319" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
     </row>
     <row r="1320">
       <c r="A1320" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
     </row>
     <row r="1321">
       <c r="A1321" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
     </row>
     <row r="1322">
       <c r="A1322" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
     </row>
     <row r="1323">
       <c r="A1323" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
     </row>
     <row r="1324">
       <c r="A1324" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
     </row>
     <row r="1325">
       <c r="A1325" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
     </row>
     <row r="1326">
       <c r="A1326" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
     </row>
     <row r="1327">
       <c r="A1327" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
     </row>
     <row r="1328">
       <c r="A1328" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
     </row>
     <row r="1329">
       <c r="A1329" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
     </row>
     <row r="1330">
       <c r="A1330" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
     </row>
     <row r="1331">
       <c r="A1331" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
     </row>
     <row r="1332">
       <c r="A1332" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
     </row>
     <row r="1333">
       <c r="A1333" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
     </row>
     <row r="1334">
       <c r="A1334" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
     </row>
     <row r="1335">
       <c r="A1335" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
     </row>
     <row r="1336">
       <c r="A1336" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
     </row>
     <row r="1337">
       <c r="A1337" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
     </row>
     <row r="1338">
       <c r="A1338" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
     </row>
     <row r="1339">
       <c r="A1339" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
     </row>
     <row r="1340">
       <c r="A1340" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
     </row>
     <row r="1341">
       <c r="A1341" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
     </row>
     <row r="1342">
       <c r="A1342" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
     </row>
     <row r="1343">
       <c r="A1343" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
     </row>
     <row r="1344">
       <c r="A1344" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
     </row>
     <row r="1345">
       <c r="A1345" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
     </row>
     <row r="1346">
       <c r="A1346" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
     </row>
     <row r="1347">
       <c r="A1347" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
     </row>
     <row r="1348">
       <c r="A1348" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
     </row>
     <row r="1349">
       <c r="A1349" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
     </row>
     <row r="1350">
       <c r="A1350" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
     </row>
     <row r="1351">
       <c r="A1351" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
     </row>
     <row r="1352">
       <c r="A1352" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
     </row>
     <row r="1353">
       <c r="A1353" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
     </row>
     <row r="1354">
       <c r="A1354" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
     </row>
     <row r="1355">
       <c r="A1355" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
     </row>
     <row r="1356">
       <c r="A1356" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
     </row>
     <row r="1357">
       <c r="A1357" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
     </row>
     <row r="1358">
       <c r="A1358" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
     </row>
     <row r="1359">
       <c r="A1359" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
     </row>
     <row r="1360">
       <c r="A1360" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
     </row>
     <row r="1361">
       <c r="A1361" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
     </row>
     <row r="1362">
       <c r="A1362" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
     </row>
     <row r="1363">
       <c r="A1363" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
     </row>
     <row r="1364">
       <c r="A1364" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
     </row>
     <row r="1365">
       <c r="A1365" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
     </row>
     <row r="1366">
       <c r="A1366" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
     </row>
     <row r="1367">
       <c r="A1367" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
     </row>
     <row r="1368">
       <c r="A1368" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
     </row>
     <row r="1369">
       <c r="A1369" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
     </row>
     <row r="1370">
       <c r="A1370" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
     </row>
     <row r="1371">
       <c r="A1371" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
     </row>
     <row r="1372">
       <c r="A1372" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
     </row>
     <row r="1373">
       <c r="A1373" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
     </row>
     <row r="1374">
       <c r="A1374" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
     </row>
     <row r="1375">
       <c r="A1375" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
     </row>
     <row r="1376">
       <c r="A1376" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
     </row>
     <row r="1377">
       <c r="A1377" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
     </row>
     <row r="1378">
       <c r="A1378" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
     </row>
     <row r="1379">
       <c r="A1379" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
     </row>
     <row r="1380">
       <c r="A1380" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
     </row>
     <row r="1381">
       <c r="A1381" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
     </row>
     <row r="1382">
       <c r="A1382" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
     </row>
     <row r="1383">
       <c r="A1383" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
     </row>
     <row r="1384">
       <c r="A1384" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
     </row>
     <row r="1385">
       <c r="A1385" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
     </row>
     <row r="1386">
       <c r="A1386" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
     </row>
     <row r="1387">
       <c r="A1387" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
     </row>
     <row r="1388">
       <c r="A1388" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
     </row>
     <row r="1389">
       <c r="A1389" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
     </row>
     <row r="1390">
       <c r="A1390" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
     </row>
     <row r="1391">
       <c r="A1391" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
     </row>
     <row r="1392">
       <c r="A1392" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
     </row>
     <row r="1393">
       <c r="A1393" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
     </row>
     <row r="1394">
       <c r="A1394" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
     </row>
     <row r="1395">
       <c r="A1395" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
     </row>
     <row r="1396">
       <c r="A1396" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
     </row>
     <row r="1397">
       <c r="A1397" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
     </row>
     <row r="1398">
       <c r="A1398" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
@@ -40972,7 +40972,7 @@
     </row>
     <row r="1399">
       <c r="A1399" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
     </row>
     <row r="1400">
       <c r="A1400" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
@@ -41030,7 +41030,7 @@
     </row>
     <row r="1401">
       <c r="A1401" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
     </row>
     <row r="1402">
       <c r="A1402" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
     </row>
     <row r="1403">
       <c r="A1403" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
     </row>
     <row r="1404">
       <c r="A1404" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
     </row>
     <row r="1405">
       <c r="A1405" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
     </row>
     <row r="1406">
       <c r="A1406" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
     </row>
     <row r="1407">
       <c r="A1407" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
     </row>
     <row r="1408">
       <c r="A1408" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
     </row>
     <row r="1409">
       <c r="A1409" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
     </row>
     <row r="1410">
       <c r="A1410" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
     </row>
     <row r="1411">
       <c r="A1411" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
     </row>
     <row r="1412">
       <c r="A1412" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
     </row>
     <row r="1413">
       <c r="A1413" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
     </row>
     <row r="1414">
       <c r="A1414" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
     </row>
     <row r="1415">
       <c r="A1415" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
     </row>
     <row r="1416">
       <c r="A1416" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
     </row>
     <row r="1417">
       <c r="A1417" s="1" t="n">
-        <v>46139.61802309471</v>
+        <v>46139.61802309028</v>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
@@ -41516,6 +41516,3428 @@
         <v>1</v>
       </c>
       <c r="G1417" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1418" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+        </is>
+      </c>
+      <c r="D1419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>AG2 /EBTA</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>AG2 /EBTA</t>
+        </is>
+      </c>
+      <c r="D1420" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS SA</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS SA</t>
+        </is>
+      </c>
+      <c r="D1421" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>AMDOCS BRASIL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>AMDOCS BRASIL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1422" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>AMPLA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>AMPLA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>ANGLOGOLD ASHANTI</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>ANGLOGOLD ASHANTI</t>
+        </is>
+      </c>
+      <c r="D1424" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>AON BENFIELD</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>AON BENFIELD</t>
+        </is>
+      </c>
+      <c r="D1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>BAIN BRASIL</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>BAIN BRASIL</t>
+        </is>
+      </c>
+      <c r="D1426" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>BANCO CNH CAPITAL</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>BANCO CNH CAPITAL</t>
+        </is>
+      </c>
+      <c r="D1427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>BANCO DE INVESTIMENTOS CREDIT SUISS</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>BANCO DE INVESTIMENTOS CREDIT SUISS</t>
+        </is>
+      </c>
+      <c r="D1428" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>BANCO FIDIS SA</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>BANCO FIDIS SA</t>
+        </is>
+      </c>
+      <c r="D1429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>BMW DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>BMW DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1430" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>BMW FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>BMW FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="D1431" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>BORDA DO CAMPO MOTORES</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>BORDA DO CAMPO MOTORES</t>
+        </is>
+      </c>
+      <c r="D1432" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>CAMERON TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>CAMERON TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="D1433" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>CANAL BRAZIL SA</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>CANAL BRAZIL SA</t>
+        </is>
+      </c>
+      <c r="D1434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>CDSA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>CDSA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>CEG EBTA</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>CEG EBTA</t>
+        </is>
+      </c>
+      <c r="D1436" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>CHAPADA</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>CHAPADA</t>
+        </is>
+      </c>
+      <c r="D1437" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+        </is>
+      </c>
+      <c r="D1438" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRAS</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRAS</t>
+        </is>
+      </c>
+      <c r="D1439" t="n">
+        <v>50</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>291</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D1440" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>CNH LATIN EVENTOS</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>CNH LATIN EVENTOS</t>
+        </is>
+      </c>
+      <c r="D1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>COELCE/EBTA</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>COELCE/EBTA</t>
+        </is>
+      </c>
+      <c r="D1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>COLGATE PALMOLIVE</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>COLGATE PALMOLIVE</t>
+        </is>
+      </c>
+      <c r="D1443" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+        </is>
+      </c>
+      <c r="D1444" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+        </is>
+      </c>
+      <c r="D1445" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>DELL COMPUTADORES</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>DELL COMPUTADORES</t>
+        </is>
+      </c>
+      <c r="D1446" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>DPZ&amp;T COMUNICACOES</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>DPZ&amp;T COMUNICACOES</t>
+        </is>
+      </c>
+      <c r="D1447" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="D1448" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>EDP RENOVAVEIS CWT</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>EDP RENOVAVEIS CWT</t>
+        </is>
+      </c>
+      <c r="D1449" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="D1450" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 24/EBTA</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 24/EBTA</t>
+        </is>
+      </c>
+      <c r="D1451" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>ENEL EBTA</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>ENEL EBTA</t>
+        </is>
+      </c>
+      <c r="D1452" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>ENERGIAS DO BR</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>ENERGIAS DO BR</t>
+        </is>
+      </c>
+      <c r="D1453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>ENGIE BRASIL SOLUCO</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>ENGIE BRASIL SOLUCO</t>
+        </is>
+      </c>
+      <c r="D1454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>ENGIE CONSULTORIA E GESTAO DE ENERG</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>ENGIE CONSULTORIA E GESTAO DE ENERG</t>
+        </is>
+      </c>
+      <c r="D1455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>ENGIE GERENCIAMENTO DE ENERGIA LTDA</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>ENGIE GERENCIAMENTO DE ENERGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D1456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+        </is>
+      </c>
+      <c r="D1457" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>ESPORTE INTERATIVO</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>ESPORTE INTERATIVO</t>
+        </is>
+      </c>
+      <c r="D1458" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>FCA FIAT CHRYSLER</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>FCA FIAT CHRYSLER</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>FD DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>FD DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>FIAT AUTO GOIANA</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>FIAT AUTO GOIANA</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>FITCH RATINGS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>FITCH RATINGS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>GSK CONSUMO TRES</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>GSK CONSUMO TRES</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>GSK EVENTOS</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>GSK EVENTOS</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>159</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>GUERBET IMAGEM</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>GUERBET IMAGEM</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>GYRODATA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>GYRODATA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D1478" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>HUSQVARNA BR</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>HUSQVARNA BR</t>
+        </is>
+      </c>
+      <c r="D1479" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>IDV BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>IDV BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1480" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>IMPALA COSMETICOS/EBTA</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>IMPALA COSMETICOS/EBTA</t>
+        </is>
+      </c>
+      <c r="D1481" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>IPIRANGA PRODUTOS DE PETROLEO S A</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>IPIRANGA PRODUTOS DE PETROLEO S A</t>
+        </is>
+      </c>
+      <c r="D1482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+        </is>
+      </c>
+      <c r="D1483" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+        </is>
+      </c>
+      <c r="D1484" t="n">
+        <v>47</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>LEO BURNETT NEO/EBTA</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>LEO BURNETT NEO/EBTA</t>
+        </is>
+      </c>
+      <c r="D1485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D1486" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>MCKINSEY</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>MCKINSEY</t>
+        </is>
+      </c>
+      <c r="D1487" t="n">
+        <v>64</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>148</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>MCKINSEY EBTA</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>MCKINSEY EBTA</t>
+        </is>
+      </c>
+      <c r="D1488" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D1490" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS JF LTDA</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS JF LTDA</t>
+        </is>
+      </c>
+      <c r="D1491" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS SA</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS SA</t>
+        </is>
+      </c>
+      <c r="D1492" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>MORGAN STANLEY CTVM S A</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>MORGAN STANLEY CTVM S A</t>
+        </is>
+      </c>
+      <c r="D1493" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+        </is>
+      </c>
+      <c r="D1494" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>MOTOROLA MOBIL</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>MOTOROLA MOBIL</t>
+        </is>
+      </c>
+      <c r="D1495" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>MRM BRASIL PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>MRM BRASIL PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1496" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1497" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+        </is>
+      </c>
+      <c r="D1498" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+        </is>
+      </c>
+      <c r="D1499" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>ON HIGHWAY BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>ON HIGHWAY BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1500" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+        </is>
+      </c>
+      <c r="D1501" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+        </is>
+      </c>
+      <c r="D1502" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>PRATIL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>PRATIL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1503" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+        </is>
+      </c>
+      <c r="D1504" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>PROSEGUR PAY CONSULTORIA EM TECNOLO</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>PROSEGUR PAY CONSULTORIA EM TECNOLO</t>
+        </is>
+      </c>
+      <c r="D1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D1506" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>RENAULT DO BRASIL S A</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>RENAULT DO BRASIL S A</t>
+        </is>
+      </c>
+      <c r="D1507" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+        </is>
+      </c>
+      <c r="D1508" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>SCHWEITZER MAU</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>SCHWEITZER MAU</t>
+        </is>
+      </c>
+      <c r="D1509" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>SDOISPUBLICOM EBTA</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>SDOISPUBLICOM EBTA</t>
+        </is>
+      </c>
+      <c r="D1510" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+        </is>
+      </c>
+      <c r="D1512" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>SENFFNET INSTITUICAO DE PAGAMENTO L</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>SENFFNET INSTITUICAO DE PAGAMENTO L</t>
+        </is>
+      </c>
+      <c r="D1513" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>SERRA GRANDE</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>SERRA GRANDE</t>
+        </is>
+      </c>
+      <c r="D1514" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>SIDEL DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>SIDEL DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1515" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>SITA INC DO BRASIL /EBTA</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>SITA INC DO BRASIL /EBTA</t>
+        </is>
+      </c>
+      <c r="D1516" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>TALENT MARCEL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>TALENT MARCEL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1517" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>TBB PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>TBB PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1518" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>TENNECO AUTOMOTIVE BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>TENNECO AUTOMOTIVE BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1519" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>TOWERS WATSON</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>TOWERS WATSON</t>
+        </is>
+      </c>
+      <c r="D1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>TRACTEBEL ENGI</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>TRACTEBEL ENGI</t>
+        </is>
+      </c>
+      <c r="D1521" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+        </is>
+      </c>
+      <c r="D1522" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+        </is>
+      </c>
+      <c r="D1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>TSA/EBTA  - VTS</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>TSA/EBTA  - VTS</t>
+        </is>
+      </c>
+      <c r="D1524" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+        </is>
+      </c>
+      <c r="D1525" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+        </is>
+      </c>
+      <c r="D1526" t="n">
+        <v>21</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
+        </is>
+      </c>
+      <c r="D1527" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+        </is>
+      </c>
+      <c r="D1528" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1529" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+        </is>
+      </c>
+      <c r="D1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+        </is>
+      </c>
+      <c r="D1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>WARNER BROS SOUTH INC</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>WARNER BROS SOUTH INC</t>
+        </is>
+      </c>
+      <c r="D1532" t="n">
+        <v>38</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>WILLIS AFFINITY</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>WILLIS AFFINITY</t>
+        </is>
+      </c>
+      <c r="D1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>WILLIS CORRETO</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>WILLIS CORRETO</t>
+        </is>
+      </c>
+      <c r="D1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="1" t="n">
+        <v>46139.74981264526</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>WILLIS RESSEGUROS</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>WILLIS RESSEGUROS</t>
+        </is>
+      </c>
+      <c r="D1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1535" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1535"/>
+  <dimension ref="A1:G1771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41523,7 +41523,7 @@
     </row>
     <row r="1418">
       <c r="A1418" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
     </row>
     <row r="1419">
       <c r="A1419" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
     </row>
     <row r="1420">
       <c r="A1420" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
     </row>
     <row r="1421">
       <c r="A1421" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
     </row>
     <row r="1422">
       <c r="A1422" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
     </row>
     <row r="1423">
       <c r="A1423" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
     </row>
     <row r="1424">
       <c r="A1424" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
     </row>
     <row r="1425">
       <c r="A1425" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
     </row>
     <row r="1426">
       <c r="A1426" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
     </row>
     <row r="1427">
       <c r="A1427" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
     </row>
     <row r="1428">
       <c r="A1428" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
     </row>
     <row r="1429">
       <c r="A1429" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
     </row>
     <row r="1430">
       <c r="A1430" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
     </row>
     <row r="1431">
       <c r="A1431" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
     </row>
     <row r="1432">
       <c r="A1432" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
     </row>
     <row r="1433">
       <c r="A1433" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
     </row>
     <row r="1434">
       <c r="A1434" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
     </row>
     <row r="1435">
       <c r="A1435" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
     </row>
     <row r="1436">
       <c r="A1436" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
     </row>
     <row r="1437">
       <c r="A1437" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
     </row>
     <row r="1438">
       <c r="A1438" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
     </row>
     <row r="1439">
       <c r="A1439" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
     </row>
     <row r="1440">
       <c r="A1440" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
     </row>
     <row r="1441">
       <c r="A1441" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
     </row>
     <row r="1442">
       <c r="A1442" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
     </row>
     <row r="1443">
       <c r="A1443" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
     </row>
     <row r="1444">
       <c r="A1444" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
     </row>
     <row r="1445">
       <c r="A1445" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
     </row>
     <row r="1446">
       <c r="A1446" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
     </row>
     <row r="1447">
       <c r="A1447" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
     </row>
     <row r="1448">
       <c r="A1448" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
     </row>
     <row r="1449">
       <c r="A1449" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
     </row>
     <row r="1450">
       <c r="A1450" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
     </row>
     <row r="1451">
       <c r="A1451" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
     </row>
     <row r="1452">
       <c r="A1452" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
     </row>
     <row r="1453">
       <c r="A1453" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
     </row>
     <row r="1454">
       <c r="A1454" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
     </row>
     <row r="1455">
       <c r="A1455" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
     </row>
     <row r="1456">
       <c r="A1456" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
     </row>
     <row r="1457">
       <c r="A1457" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
     </row>
     <row r="1458">
       <c r="A1458" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
     </row>
     <row r="1459">
       <c r="A1459" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
     </row>
     <row r="1460">
       <c r="A1460" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
     </row>
     <row r="1461">
       <c r="A1461" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
     </row>
     <row r="1462">
       <c r="A1462" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
     </row>
     <row r="1463">
       <c r="A1463" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
     </row>
     <row r="1464">
       <c r="A1464" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
     </row>
     <row r="1465">
       <c r="A1465" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
     </row>
     <row r="1466">
       <c r="A1466" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
     </row>
     <row r="1467">
       <c r="A1467" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
     </row>
     <row r="1468">
       <c r="A1468" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
     </row>
     <row r="1469">
       <c r="A1469" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
     </row>
     <row r="1470">
       <c r="A1470" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
     </row>
     <row r="1471">
       <c r="A1471" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
     </row>
     <row r="1472">
       <c r="A1472" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
     </row>
     <row r="1473">
       <c r="A1473" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
     </row>
     <row r="1474">
       <c r="A1474" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
     </row>
     <row r="1475">
       <c r="A1475" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
     </row>
     <row r="1476">
       <c r="A1476" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
     </row>
     <row r="1477">
       <c r="A1477" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
     </row>
     <row r="1478">
       <c r="A1478" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
     </row>
     <row r="1479">
       <c r="A1479" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
     </row>
     <row r="1480">
       <c r="A1480" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
     </row>
     <row r="1481">
       <c r="A1481" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
     </row>
     <row r="1482">
       <c r="A1482" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
     </row>
     <row r="1483">
       <c r="A1483" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
     </row>
     <row r="1484">
       <c r="A1484" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
     </row>
     <row r="1485">
       <c r="A1485" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
     </row>
     <row r="1486">
       <c r="A1486" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
     </row>
     <row r="1487">
       <c r="A1487" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
     </row>
     <row r="1488">
       <c r="A1488" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
     </row>
     <row r="1489">
       <c r="A1489" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
     </row>
     <row r="1490">
       <c r="A1490" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
     </row>
     <row r="1491">
       <c r="A1491" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
     </row>
     <row r="1492">
       <c r="A1492" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
     </row>
     <row r="1493">
       <c r="A1493" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
     </row>
     <row r="1494">
       <c r="A1494" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
     </row>
     <row r="1495">
       <c r="A1495" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
     </row>
     <row r="1496">
       <c r="A1496" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
     </row>
     <row r="1497">
       <c r="A1497" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
     </row>
     <row r="1498">
       <c r="A1498" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
     </row>
     <row r="1499">
       <c r="A1499" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
     </row>
     <row r="1500">
       <c r="A1500" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
     </row>
     <row r="1501">
       <c r="A1501" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
     </row>
     <row r="1502">
       <c r="A1502" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
     </row>
     <row r="1503">
       <c r="A1503" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
     </row>
     <row r="1504">
       <c r="A1504" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
     </row>
     <row r="1505">
       <c r="A1505" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
     </row>
     <row r="1506">
       <c r="A1506" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
     </row>
     <row r="1507">
       <c r="A1507" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
     </row>
     <row r="1508">
       <c r="A1508" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
     </row>
     <row r="1509">
       <c r="A1509" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
     </row>
     <row r="1510">
       <c r="A1510" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
     </row>
     <row r="1511">
       <c r="A1511" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
     </row>
     <row r="1512">
       <c r="A1512" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
     </row>
     <row r="1513">
       <c r="A1513" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
     </row>
     <row r="1514">
       <c r="A1514" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
     </row>
     <row r="1515">
       <c r="A1515" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
     </row>
     <row r="1516">
       <c r="A1516" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
     </row>
     <row r="1517">
       <c r="A1517" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
     </row>
     <row r="1518">
       <c r="A1518" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
     </row>
     <row r="1519">
       <c r="A1519" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
     </row>
     <row r="1520">
       <c r="A1520" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
     </row>
     <row r="1521">
       <c r="A1521" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
     </row>
     <row r="1522">
       <c r="A1522" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
     </row>
     <row r="1523">
       <c r="A1523" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
     </row>
     <row r="1524">
       <c r="A1524" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
     </row>
     <row r="1525">
       <c r="A1525" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
     </row>
     <row r="1526">
       <c r="A1526" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
     </row>
     <row r="1527">
       <c r="A1527" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
     </row>
     <row r="1528">
       <c r="A1528" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
     </row>
     <row r="1529">
       <c r="A1529" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
     </row>
     <row r="1530">
       <c r="A1530" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
     </row>
     <row r="1531">
       <c r="A1531" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
     </row>
     <row r="1532">
       <c r="A1532" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
     </row>
     <row r="1533">
       <c r="A1533" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
     </row>
     <row r="1534">
       <c r="A1534" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
     </row>
     <row r="1535">
       <c r="A1535" s="1" t="n">
-        <v>46139.74981264526</v>
+        <v>46139.74981265047</v>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
@@ -44938,6 +44938,6850 @@
         <v>1</v>
       </c>
       <c r="G1535" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1536" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+        </is>
+      </c>
+      <c r="D1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>AG2 /EBTA</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>AG2 /EBTA</t>
+        </is>
+      </c>
+      <c r="D1538" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS SA</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS SA</t>
+        </is>
+      </c>
+      <c r="D1539" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>AMDOCS BRASIL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>AMDOCS BRASIL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1540" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>AMPLA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>AMPLA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1541" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>ANGLOGOLD ASHANTI</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>ANGLOGOLD ASHANTI</t>
+        </is>
+      </c>
+      <c r="D1542" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>AON BENFIELD</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>AON BENFIELD</t>
+        </is>
+      </c>
+      <c r="D1543" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>BAIN BRASIL</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>BAIN BRASIL</t>
+        </is>
+      </c>
+      <c r="D1544" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>BANCO CNH CAPITAL</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>BANCO CNH CAPITAL</t>
+        </is>
+      </c>
+      <c r="D1545" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>BANCO DE INVESTIMENTOS CREDIT SUISS</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>BANCO DE INVESTIMENTOS CREDIT SUISS</t>
+        </is>
+      </c>
+      <c r="D1546" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>BANCO FIDIS SA</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>BANCO FIDIS SA</t>
+        </is>
+      </c>
+      <c r="D1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>BMW DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>BMW DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1548" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>BMW FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>BMW FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="D1549" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>BORDA DO CAMPO MOTORES</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>BORDA DO CAMPO MOTORES</t>
+        </is>
+      </c>
+      <c r="D1550" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>CAMERON TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>CAMERON TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="D1551" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>CANAL BRAZIL SA</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>CANAL BRAZIL SA</t>
+        </is>
+      </c>
+      <c r="D1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>CDSA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>CDSA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>CEG EBTA</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>CEG EBTA</t>
+        </is>
+      </c>
+      <c r="D1554" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>CHAPADA</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>CHAPADA</t>
+        </is>
+      </c>
+      <c r="D1555" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+        </is>
+      </c>
+      <c r="D1556" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRAS</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRAS</t>
+        </is>
+      </c>
+      <c r="D1557" t="n">
+        <v>50</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>291</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D1558" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>CNH LATIN EVENTOS</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>CNH LATIN EVENTOS</t>
+        </is>
+      </c>
+      <c r="D1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>COELCE/EBTA</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>COELCE/EBTA</t>
+        </is>
+      </c>
+      <c r="D1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>COLGATE PALMOLIVE</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>COLGATE PALMOLIVE</t>
+        </is>
+      </c>
+      <c r="D1561" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+        </is>
+      </c>
+      <c r="D1562" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+        </is>
+      </c>
+      <c r="D1563" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>DELL COMPUTADORES</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>DELL COMPUTADORES</t>
+        </is>
+      </c>
+      <c r="D1564" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>DPZ&amp;T COMUNICACOES</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>DPZ&amp;T COMUNICACOES</t>
+        </is>
+      </c>
+      <c r="D1565" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="D1566" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>EDP RENOVAVEIS CWT</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>EDP RENOVAVEIS CWT</t>
+        </is>
+      </c>
+      <c r="D1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="D1568" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 24/EBTA</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 24/EBTA</t>
+        </is>
+      </c>
+      <c r="D1569" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>ENEL EBTA</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>ENEL EBTA</t>
+        </is>
+      </c>
+      <c r="D1570" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>ENERGIAS DO BR</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>ENERGIAS DO BR</t>
+        </is>
+      </c>
+      <c r="D1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>ENGIE BRASIL SOLUCO</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>ENGIE BRASIL SOLUCO</t>
+        </is>
+      </c>
+      <c r="D1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>ENGIE CONSULTORIA E GESTAO DE ENERG</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>ENGIE CONSULTORIA E GESTAO DE ENERG</t>
+        </is>
+      </c>
+      <c r="D1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>ENGIE GERENCIAMENTO DE ENERGIA LTDA</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>ENGIE GERENCIAMENTO DE ENERGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+        </is>
+      </c>
+      <c r="D1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>ESPORTE INTERATIVO</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>ESPORTE INTERATIVO</t>
+        </is>
+      </c>
+      <c r="D1576" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>FCA FIAT CHRYSLER</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>FCA FIAT CHRYSLER</t>
+        </is>
+      </c>
+      <c r="D1577" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>FD DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>FD DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1578" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>FIAT AUTO GOIANA</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>FIAT AUTO GOIANA</t>
+        </is>
+      </c>
+      <c r="D1579" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+        </is>
+      </c>
+      <c r="D1580" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>FITCH RATINGS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>FITCH RATINGS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1581" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+        </is>
+      </c>
+      <c r="D1582" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1583" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="D1584" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="D1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+        </is>
+      </c>
+      <c r="D1586" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+        </is>
+      </c>
+      <c r="D1587" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>GSK CONSUMO TRES</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>GSK CONSUMO TRES</t>
+        </is>
+      </c>
+      <c r="D1588" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>GSK EVENTOS</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>GSK EVENTOS</t>
+        </is>
+      </c>
+      <c r="D1589" t="n">
+        <v>159</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>GUERBET IMAGEM</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>GUERBET IMAGEM</t>
+        </is>
+      </c>
+      <c r="D1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>GYRODATA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>GYRODATA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+        </is>
+      </c>
+      <c r="D1592" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D1593" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D1594" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+        </is>
+      </c>
+      <c r="D1595" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D1596" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>HUSQVARNA BR</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>HUSQVARNA BR</t>
+        </is>
+      </c>
+      <c r="D1597" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>IDV BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>IDV BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1598" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>IMPALA COSMETICOS/EBTA</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>IMPALA COSMETICOS/EBTA</t>
+        </is>
+      </c>
+      <c r="D1599" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>IPIRANGA PRODUTOS DE PETROLEO S A</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>IPIRANGA PRODUTOS DE PETROLEO S A</t>
+        </is>
+      </c>
+      <c r="D1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+        </is>
+      </c>
+      <c r="D1601" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+        </is>
+      </c>
+      <c r="D1602" t="n">
+        <v>47</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>LEO BURNETT NEO/EBTA</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>LEO BURNETT NEO/EBTA</t>
+        </is>
+      </c>
+      <c r="D1603" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D1604" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>MCKINSEY</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>MCKINSEY</t>
+        </is>
+      </c>
+      <c r="D1605" t="n">
+        <v>63</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>148</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>MCKINSEY EBTA</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>MCKINSEY EBTA</t>
+        </is>
+      </c>
+      <c r="D1606" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1607" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D1608" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS JF LTDA</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS JF LTDA</t>
+        </is>
+      </c>
+      <c r="D1609" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS SA</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS SA</t>
+        </is>
+      </c>
+      <c r="D1610" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>MORGAN STANLEY CTVM S A</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>MORGAN STANLEY CTVM S A</t>
+        </is>
+      </c>
+      <c r="D1611" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+        </is>
+      </c>
+      <c r="D1612" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>MOTOROLA MOBIL</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>MOTOROLA MOBIL</t>
+        </is>
+      </c>
+      <c r="D1613" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>MRM BRASIL PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>MRM BRASIL PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1614" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1615" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+        </is>
+      </c>
+      <c r="D1616" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+        </is>
+      </c>
+      <c r="D1617" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>ON HIGHWAY BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>ON HIGHWAY BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1618" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+        </is>
+      </c>
+      <c r="D1619" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+        </is>
+      </c>
+      <c r="D1620" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>PRATIL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>PRATIL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1621" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+        </is>
+      </c>
+      <c r="D1622" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>PROSEGUR PAY CONSULTORIA EM TECNOLO</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>PROSEGUR PAY CONSULTORIA EM TECNOLO</t>
+        </is>
+      </c>
+      <c r="D1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D1624" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>RENAULT DO BRASIL S A</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>RENAULT DO BRASIL S A</t>
+        </is>
+      </c>
+      <c r="D1625" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+        </is>
+      </c>
+      <c r="D1626" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>SCHWEITZER MAU</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>SCHWEITZER MAU</t>
+        </is>
+      </c>
+      <c r="D1627" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>SDOISPUBLICOM EBTA</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>SDOISPUBLICOM EBTA</t>
+        </is>
+      </c>
+      <c r="D1628" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+        </is>
+      </c>
+      <c r="D1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+        </is>
+      </c>
+      <c r="D1630" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>SENFFNET INSTITUICAO DE PAGAMENTO L</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>SENFFNET INSTITUICAO DE PAGAMENTO L</t>
+        </is>
+      </c>
+      <c r="D1631" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>SERRA GRANDE</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>SERRA GRANDE</t>
+        </is>
+      </c>
+      <c r="D1632" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>SIDEL DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>SIDEL DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1633" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>SITA INC DO BRASIL /EBTA</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>SITA INC DO BRASIL /EBTA</t>
+        </is>
+      </c>
+      <c r="D1634" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>TALENT MARCEL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>TALENT MARCEL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1635" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>TBB PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>TBB PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1636" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>TENNECO AUTOMOTIVE BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>TENNECO AUTOMOTIVE BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1637" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>TOWERS WATSON</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>TOWERS WATSON</t>
+        </is>
+      </c>
+      <c r="D1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>TRACTEBEL ENGI</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>TRACTEBEL ENGI</t>
+        </is>
+      </c>
+      <c r="D1639" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+        </is>
+      </c>
+      <c r="D1640" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+        </is>
+      </c>
+      <c r="D1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>TSA/EBTA  - VTS</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>TSA/EBTA  - VTS</t>
+        </is>
+      </c>
+      <c r="D1642" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+        </is>
+      </c>
+      <c r="D1643" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+        </is>
+      </c>
+      <c r="D1644" t="n">
+        <v>21</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
+        </is>
+      </c>
+      <c r="D1645" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+        </is>
+      </c>
+      <c r="D1646" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1647" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+        </is>
+      </c>
+      <c r="D1648" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+        </is>
+      </c>
+      <c r="D1649" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>WARNER BROS SOUTH INC</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>WARNER BROS SOUTH INC</t>
+        </is>
+      </c>
+      <c r="D1650" t="n">
+        <v>38</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>WILLIS AFFINITY</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>WILLIS AFFINITY</t>
+        </is>
+      </c>
+      <c r="D1651" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>WILLIS CORRETO</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>WILLIS CORRETO</t>
+        </is>
+      </c>
+      <c r="D1652" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="1" t="n">
+        <v>46140.44566571759</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>WILLIS RESSEGUROS</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>WILLIS RESSEGUROS</t>
+        </is>
+      </c>
+      <c r="D1653" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1654" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+        </is>
+      </c>
+      <c r="D1655" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>AG2 /EBTA</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>AG2 /EBTA</t>
+        </is>
+      </c>
+      <c r="D1656" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS SA</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS SA</t>
+        </is>
+      </c>
+      <c r="D1657" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>AMDOCS BRASIL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>AMDOCS BRASIL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1658" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>AMPLA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>AMPLA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1659" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>ANGLOGOLD ASHANTI</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>ANGLOGOLD ASHANTI</t>
+        </is>
+      </c>
+      <c r="D1660" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>AON BENFIELD</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>AON BENFIELD</t>
+        </is>
+      </c>
+      <c r="D1661" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>BAIN BRASIL</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>BAIN BRASIL</t>
+        </is>
+      </c>
+      <c r="D1662" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>BANCO CNH CAPITAL</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>BANCO CNH CAPITAL</t>
+        </is>
+      </c>
+      <c r="D1663" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>BANCO DE INVESTIMENTOS CREDIT SUISS</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>BANCO DE INVESTIMENTOS CREDIT SUISS</t>
+        </is>
+      </c>
+      <c r="D1664" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>BANCO FIDIS SA</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>BANCO FIDIS SA</t>
+        </is>
+      </c>
+      <c r="D1665" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>BMW DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>BMW DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1666" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>BMW FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>BMW FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="D1667" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>BORDA DO CAMPO MOTORES</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>BORDA DO CAMPO MOTORES</t>
+        </is>
+      </c>
+      <c r="D1668" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>CAMERON TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>CAMERON TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="D1669" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>CANAL BRAZIL SA</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>CANAL BRAZIL SA</t>
+        </is>
+      </c>
+      <c r="D1670" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>CDSA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>CDSA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1671" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>CEG EBTA</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>CEG EBTA</t>
+        </is>
+      </c>
+      <c r="D1672" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>CHAPADA</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>CHAPADA</t>
+        </is>
+      </c>
+      <c r="D1673" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+        </is>
+      </c>
+      <c r="D1674" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRAS</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRAS</t>
+        </is>
+      </c>
+      <c r="D1675" t="n">
+        <v>50</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>291</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D1676" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>CNH LATIN EVENTOS</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>CNH LATIN EVENTOS</t>
+        </is>
+      </c>
+      <c r="D1677" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>COELCE/EBTA</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>COELCE/EBTA</t>
+        </is>
+      </c>
+      <c r="D1678" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>COLGATE PALMOLIVE</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>COLGATE PALMOLIVE</t>
+        </is>
+      </c>
+      <c r="D1679" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+        </is>
+      </c>
+      <c r="D1680" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+        </is>
+      </c>
+      <c r="D1681" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>DELL COMPUTADORES</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>DELL COMPUTADORES</t>
+        </is>
+      </c>
+      <c r="D1682" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>DPZ&amp;T COMUNICACOES</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>DPZ&amp;T COMUNICACOES</t>
+        </is>
+      </c>
+      <c r="D1683" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="D1684" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>EDP RENOVAVEIS CWT</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>EDP RENOVAVEIS CWT</t>
+        </is>
+      </c>
+      <c r="D1685" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="D1686" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 24/EBTA</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 24/EBTA</t>
+        </is>
+      </c>
+      <c r="D1687" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>ENEL EBTA</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>ENEL EBTA</t>
+        </is>
+      </c>
+      <c r="D1688" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>ENERGIAS DO BR</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>ENERGIAS DO BR</t>
+        </is>
+      </c>
+      <c r="D1689" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>ENGIE BRASIL SOLUCO</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>ENGIE BRASIL SOLUCO</t>
+        </is>
+      </c>
+      <c r="D1690" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>ENGIE CONSULTORIA E GESTAO DE ENERG</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>ENGIE CONSULTORIA E GESTAO DE ENERG</t>
+        </is>
+      </c>
+      <c r="D1691" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>ENGIE GERENCIAMENTO DE ENERGIA LTDA</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>ENGIE GERENCIAMENTO DE ENERGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+        </is>
+      </c>
+      <c r="D1693" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>ESPORTE INTERATIVO</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>ESPORTE INTERATIVO</t>
+        </is>
+      </c>
+      <c r="D1694" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>FCA FIAT CHRYSLER</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>FCA FIAT CHRYSLER</t>
+        </is>
+      </c>
+      <c r="D1695" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>FD DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>FD DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1696" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>FIAT AUTO GOIANA</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>FIAT AUTO GOIANA</t>
+        </is>
+      </c>
+      <c r="D1697" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+        </is>
+      </c>
+      <c r="D1698" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>FITCH RATINGS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>FITCH RATINGS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1699" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+        </is>
+      </c>
+      <c r="D1700" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1701" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>FRESENIUS KABI</t>
+        </is>
+      </c>
+      <c r="D1702" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="D1703" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+        </is>
+      </c>
+      <c r="D1704" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+        </is>
+      </c>
+      <c r="D1705" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>106</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>GSK CONSUMO TRES</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>GSK CONSUMO TRES</t>
+        </is>
+      </c>
+      <c r="D1706" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>GSK EVENTOS</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>GSK EVENTOS</t>
+        </is>
+      </c>
+      <c r="D1707" t="n">
+        <v>159</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>102</v>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>GUERBET IMAGEM</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>GUERBET IMAGEM</t>
+        </is>
+      </c>
+      <c r="D1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>GYRODATA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>GYRODATA DO BRASIL</t>
+        </is>
+      </c>
+      <c r="D1709" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1709" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+        </is>
+      </c>
+      <c r="D1710" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D1711" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D1712" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>28</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+        </is>
+      </c>
+      <c r="D1713" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D1714" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>HUSQVARNA BR</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>HUSQVARNA BR</t>
+        </is>
+      </c>
+      <c r="D1715" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>IDV BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>IDV BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1716" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>IMPALA COSMETICOS/EBTA</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>IMPALA COSMETICOS/EBTA</t>
+        </is>
+      </c>
+      <c r="D1717" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>IPIRANGA PRODUTOS DE PETROLEO S A</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>IPIRANGA PRODUTOS DE PETROLEO S A</t>
+        </is>
+      </c>
+      <c r="D1718" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+        </is>
+      </c>
+      <c r="D1719" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+        </is>
+      </c>
+      <c r="D1720" t="n">
+        <v>47</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>LEO BURNETT NEO/EBTA</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>LEO BURNETT NEO/EBTA</t>
+        </is>
+      </c>
+      <c r="D1721" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D1722" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1722" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1722" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>MCKINSEY</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>MCKINSEY</t>
+        </is>
+      </c>
+      <c r="D1723" t="n">
+        <v>63</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>148</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>MCKINSEY EBTA</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>MCKINSEY EBTA</t>
+        </is>
+      </c>
+      <c r="D1724" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1725" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D1726" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS JF LTDA</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS JF LTDA</t>
+        </is>
+      </c>
+      <c r="D1727" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS SA</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>MINASMAQUINAS SA</t>
+        </is>
+      </c>
+      <c r="D1728" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>MORGAN STANLEY CTVM S A</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>MORGAN STANLEY CTVM S A</t>
+        </is>
+      </c>
+      <c r="D1729" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+        </is>
+      </c>
+      <c r="D1730" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>MOTOROLA MOBIL</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>MOTOROLA MOBIL</t>
+        </is>
+      </c>
+      <c r="D1731" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>MRM BRASIL PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>MRM BRASIL PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1732" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
+        </is>
+      </c>
+      <c r="D1733" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+        </is>
+      </c>
+      <c r="D1734" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+        </is>
+      </c>
+      <c r="D1735" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>ON HIGHWAY BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>ON HIGHWAY BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1736" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+        </is>
+      </c>
+      <c r="D1737" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>49</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+        </is>
+      </c>
+      <c r="D1738" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>PRATIL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>PRATIL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1739" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+        </is>
+      </c>
+      <c r="D1740" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>PROSEGUR PAY CONSULTORIA EM TECNOLO</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>PROSEGUR PAY CONSULTORIA EM TECNOLO</t>
+        </is>
+      </c>
+      <c r="D1741" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D1742" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>RENAULT DO BRASIL S A</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>RENAULT DO BRASIL S A</t>
+        </is>
+      </c>
+      <c r="D1743" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+        </is>
+      </c>
+      <c r="D1744" t="n">
+        <v>31</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>SCHWEITZER MAU</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>SCHWEITZER MAU</t>
+        </is>
+      </c>
+      <c r="D1745" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>SDOISPUBLICOM EBTA</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>SDOISPUBLICOM EBTA</t>
+        </is>
+      </c>
+      <c r="D1746" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+        </is>
+      </c>
+      <c r="D1747" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+        </is>
+      </c>
+      <c r="D1748" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>SENFFNET INSTITUICAO DE PAGAMENTO L</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>SENFFNET INSTITUICAO DE PAGAMENTO L</t>
+        </is>
+      </c>
+      <c r="D1749" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>SERRA GRANDE</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>SERRA GRANDE</t>
+        </is>
+      </c>
+      <c r="D1750" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>SIDEL DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>SIDEL DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1751" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>SITA INC DO BRASIL /EBTA</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>SITA INC DO BRASIL /EBTA</t>
+        </is>
+      </c>
+      <c r="D1752" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>TALENT MARCEL/EBTA</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>TALENT MARCEL/EBTA</t>
+        </is>
+      </c>
+      <c r="D1753" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>TBB PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>TBB PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D1754" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>TENNECO AUTOMOTIVE BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>TENNECO AUTOMOTIVE BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1755" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>TOWERS WATSON</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>TOWERS WATSON</t>
+        </is>
+      </c>
+      <c r="D1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>TRACTEBEL ENGI</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>TRACTEBEL ENGI</t>
+        </is>
+      </c>
+      <c r="D1757" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+        </is>
+      </c>
+      <c r="D1758" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+        </is>
+      </c>
+      <c r="D1759" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>TSA/EBTA  - VTS</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>TSA/EBTA  - VTS</t>
+        </is>
+      </c>
+      <c r="D1760" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+        </is>
+      </c>
+      <c r="D1761" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+        </is>
+      </c>
+      <c r="D1762" t="n">
+        <v>21</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
+        </is>
+      </c>
+      <c r="D1763" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+        </is>
+      </c>
+      <c r="D1764" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D1765" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+        </is>
+      </c>
+      <c r="D1766" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+        </is>
+      </c>
+      <c r="D1767" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>WARNER BROS SOUTH INC</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>WARNER BROS SOUTH INC</t>
+        </is>
+      </c>
+      <c r="D1768" t="n">
+        <v>38</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>WILLIS AFFINITY</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>WILLIS AFFINITY</t>
+        </is>
+      </c>
+      <c r="D1769" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>WILLIS CORRETO</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>WILLIS CORRETO</t>
+        </is>
+      </c>
+      <c r="D1770" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="1" t="n">
+        <v>46140.6998079621</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>WILLIS RESSEGUROS</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>WILLIS RESSEGUROS</t>
+        </is>
+      </c>
+      <c r="D1771" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1771" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,23 +459,23 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46154.42793541666</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAMERON TECNOLOGIA</t>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAMERON TECNOLOGIA</t>
+          <t>AAM DO BRASIL LTDA/EBTA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -488,23 +488,23 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46154.42793541666</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -517,23 +517,23 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46154.42793541666</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+          <t>AG2 /EBTA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+          <t>AG2 /EBTA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -546,23 +546,23 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AAM DO BRASIL LTDA/EBTA</t>
+          <t>ALLIANZ BR TIV NAC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AAM DO BRASIL LTDA/EBTA</t>
+          <t>ALLIANZ BR TIV NAC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -575,23 +575,23 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+          <t>ALLIANZ SEGUROS SA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADMINISTRADORA DE CONSORCIO NACIONA</t>
+          <t>ALLIANZ SEGUROS SA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -604,26 +604,26 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AG2 /EBTA</t>
+          <t>ALLIANZ TECHNOLOGY LTDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AG2 /EBTA</t>
+          <t>ALLIANZ TECHNOLOGY LTDA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -633,23 +633,23 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALLIANZ BR TIV NAC</t>
+          <t>AMGEN BIOTECNOLOGIA DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ALLIANZ BR TIV NAC</t>
+          <t>AMGEN BIOTECNOLOGIA DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -662,23 +662,23 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALLIANZ SEGUROS SA</t>
+          <t>AMPLA/EBTA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ALLIANZ SEGUROS SA</t>
+          <t>AMPLA/EBTA</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -691,26 +691,26 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALLIANZ TECHNOLOGY LTDA</t>
+          <t>ANGLOGOLD ASHANTI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ALLIANZ TECHNOLOGY LTDA</t>
+          <t>ANGLOGOLD ASHANTI</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -720,26 +720,26 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMGEN BIOTECNOLOGIA DO BRASIL LTDA</t>
+          <t>AON BENFIELD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AMGEN BIOTECNOLOGIA DO BRASIL LTDA</t>
+          <t>AON BENFIELD</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMPLA/EBTA</t>
+          <t>AON HOLDINGS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMPLA/EBTA</t>
+          <t>AON HOLDINGS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -778,23 +778,23 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANGLOGOLD ASHANTI</t>
+          <t>APS/EBTA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANGLOGOLD ASHANTI</t>
+          <t>APS/EBTA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -807,26 +807,26 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AON BENFIELD</t>
+          <t>BAIN BRASIL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AON BENFIELD</t>
+          <t>BAIN BRASIL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -836,23 +836,23 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AON HOLDINGS</t>
+          <t>BANCO HONDA S A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AON HOLDINGS</t>
+          <t>BANCO HONDA S A</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -865,23 +865,23 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APS/EBTA</t>
+          <t>BANCO MORGAN STANLEY ADM DE CARTEIR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APS/EBTA</t>
+          <t>BANCO MORGAN STANLEY ADM DE CARTEIR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -894,26 +894,26 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BAIN BRASIL</t>
+          <t>BANCO MORGAN STANLEY S A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BAIN BRASIL</t>
+          <t>BANCO MORGAN STANLEY S A</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -923,26 +923,26 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BANCO HONDA S A</t>
+          <t>BK BRASIL OPERACAO A RESTAURAN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BANCO HONDA S A</t>
+          <t>BK BRASIL OPERACAO A RESTAURAN</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -952,26 +952,26 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BANCO MORGAN STANLEY ADM DE CARTEIR</t>
+          <t>BMW DO BRASIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BANCO MORGAN STANLEY ADM DE CARTEIR</t>
+          <t>BMW DO BRASIL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,26 +981,26 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BANCO MORGAN STANLEY S A</t>
+          <t>BMW FINANCEIRA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BANCO MORGAN STANLEY S A</t>
+          <t>BMW FINANCEIRA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1010,26 +1010,26 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BK BRASIL OPERACAO A RESTAURAN</t>
+          <t>BORDA DO CAMPO MOTORES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BK BRASIL OPERACAO A RESTAURAN</t>
+          <t>BORDA DO CAMPO MOTORES</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1039,26 +1039,26 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BMW DO BRASIL</t>
+          <t>BRF S A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMW DO BRASIL</t>
+          <t>BRF S A</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1068,26 +1068,26 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BMW FINANCEIRA</t>
+          <t>CAMERON TECNOLOGIA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMW FINANCEIRA</t>
+          <t>CAMERON TECNOLOGIA</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1097,26 +1097,26 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BORDA DO CAMPO MOTORES</t>
+          <t>CEG EBTA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BORDA DO CAMPO MOTORES</t>
+          <t>CEG EBTA</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="E24" t="n">
-        <v>4</v>
-      </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1126,23 +1126,23 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BRF S A</t>
+          <t>CENAEL SA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRF S A</t>
+          <t>CENAEL SA</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1155,26 +1155,26 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CAMERON TECNOLOGIA</t>
+          <t>CENTRAL EOLICA JAU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAMERON TECNOLOGIA</t>
+          <t>CENTRAL EOLICA JAU</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1184,26 +1184,26 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CEG EBTA</t>
+          <t>CEVA FREIGHT MANAGEMENT DO BRASIL L</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CEG EBTA</t>
+          <t>CEVA FREIGHT MANAGEMENT DO BRASIL L</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1213,20 +1213,20 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CENAEL SA</t>
+          <t>CEVA LOGISTICS LTDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CENAEL SA</t>
+          <t>CEVA LOGISTICS LTDA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -1242,26 +1242,26 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CENTRAL EOLICA JAU</t>
+          <t>CHAPADA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CENTRAL EOLICA JAU</t>
+          <t>CHAPADA</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1271,20 +1271,20 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CEVA FREIGHT MANAGEMENT DO BRASIL L</t>
+          <t>CHERTO CON EMP INT NEG/E</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEVA FREIGHT MANAGEMENT DO BRASIL L</t>
+          <t>CHERTO CON EMP INT NEG/E</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1300,26 +1300,26 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CEVA LOGISTICS LTDA</t>
+          <t>CLIMAZON INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CEVA LOGISTICS LTDA</t>
+          <t>CLIMAZON INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1329,26 +1329,26 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CHAPADA</t>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CHAPADA</t>
+          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1358,26 +1358,26 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHERTO CON EMP INT NEG/E</t>
+          <t>CNH INDUSTRIAL BRAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHERTO CON EMP INT NEG/E</t>
+          <t>CNH INDUSTRIAL BRAS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1387,26 +1387,26 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLIMAZON INDUSTRIAL LTDA</t>
+          <t>CNH INDUSTRIAL BRASIL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLIMAZON INDUSTRIAL LTDA</t>
+          <t>CNH INDUSTRIAL BRASIL</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1416,20 +1416,20 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+          <t>COFELY DO BRASIL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CMA CGM DO BRASIL AGENCIA MARITIMA</t>
+          <t>COFELY DO BRASIL</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
@@ -1445,23 +1445,23 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CNH INDUSTRIAL BRAS</t>
+          <t>COLGATE PALMOLIVE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CNH INDUSTRIAL BRAS</t>
+          <t>COLGATE PALMOLIVE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -1474,26 +1474,26 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CNH INDUSTRIAL BRASIL</t>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CNH INDUSTRIAL BRASIL</t>
+          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1503,23 +1503,23 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COFELY DO BRASIL</t>
+          <t>CORSETEC - ASSESSORIA E CORRETAGEM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>COFELY DO BRASIL</t>
+          <t>CORSETEC - ASSESSORIA E CORRETAGEM</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1532,26 +1532,26 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COLGATE PALMOLIVE</t>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COLGATE PALMOLIVE</t>
+          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1561,26 +1561,26 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+          <t>DELL COMPUTADORES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>COMPANHIA PETROQUIMICA DE PERNAMBUC</t>
+          <t>DELL COMPUTADORES</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1590,20 +1590,20 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CORSETEC - ASSESSORIA E CORRETAGEM</t>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CORSETEC - ASSESSORIA E CORRETAGEM</t>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -1619,26 +1619,26 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+          <t>EBERLE EQUIP SA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CREFAZ SOCIEDADE DE CREDITO AO MICR</t>
+          <t>EBERLE EQUIP SA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1648,26 +1648,26 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DELL COMPUTADORES</t>
+          <t>EDP ESPIRITO SANTO DISTR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DELL COMPUTADORES</t>
+          <t>EDP ESPIRITO SANTO DISTR</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1677,23 +1677,23 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+          <t>EDP GRID/EBTA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+          <t>EDP GRID/EBTA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1706,23 +1706,23 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EBERLE EQUIP SA</t>
+          <t>EDP RENOVAVEIS CWT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EBERLE EQUIP SA</t>
+          <t>EDP RENOVAVEIS CWT</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1735,23 +1735,23 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EDP ESPIRITO SANTO DISTR</t>
+          <t>EDP SAO PAULO DISTRIBUIC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EDP ESPIRITO SANTO DISTR</t>
+          <t>EDP SAO PAULO DISTRIBUIC</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1764,23 +1764,23 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EDP GRID/EBTA</t>
+          <t>EDP TRANSMISSAO GOIAS SA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EDP GRID/EBTA</t>
+          <t>EDP TRANSMISSAO GOIAS SA</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1793,23 +1793,23 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EDP RENOVAVEIS CWT</t>
+          <t>ELETROPAULO 23/EBTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EDP RENOVAVEIS CWT</t>
+          <t>ELETROPAULO 23/EBTA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1822,23 +1822,23 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EDP SAO PAULO DISTRIBUIC</t>
+          <t>ELETROPAULO 24/EBTA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EDP SAO PAULO DISTRIBUIC</t>
+          <t>ELETROPAULO 24/EBTA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1851,23 +1851,23 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EDP TRANSMISSAO GOIAS SA</t>
+          <t>ENEL EBTA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EDP TRANSMISSAO GOIAS SA</t>
+          <t>ENEL EBTA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1880,23 +1880,23 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ELETROPAULO 23/EBTA</t>
+          <t>ENERGIAS DO BR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ELETROPAULO 23/EBTA</t>
+          <t>ENERGIAS DO BR</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1909,23 +1909,23 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ELETROPAULO 24/EBTA</t>
+          <t>ENGIE BRASIL SOLUCO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ELETROPAULO 24/EBTA</t>
+          <t>ENGIE BRASIL SOLUCO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1938,23 +1938,23 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ENEL EBTA</t>
+          <t>ENGIE SOLUCOES DE ILUMINACAO P</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENEL EBTA</t>
+          <t>ENGIE SOLUCOES DE ILUMINACAO P</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1967,26 +1967,26 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ENERGIAS DO BR</t>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENERGIAS DO BR</t>
+          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENGIE BRASIL SOLUCO</t>
+          <t>ESPORTE INTERATIVO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENGIE BRASIL SOLUCO</t>
+          <t>ESPORTE INTERATIVO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2025,20 +2025,20 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ENGIE SOLUCOES DE ILUMINACAO P</t>
+          <t>FCA FIAT CHRYSLER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENGIE SOLUCOES DE ILUMINACAO P</t>
+          <t>FCA FIAT CHRYSLER</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -2054,26 +2054,26 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+          <t>FD DO BRASIL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ENGIE SOLUCOES DE OPERACAO E MANUTE</t>
+          <t>FD DO BRASIL</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2083,26 +2083,26 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ESPORTE INTERATIVO</t>
+          <t>FIAT AUTO GOIANA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESPORTE INTERATIVO</t>
+          <t>FIAT AUTO GOIANA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2112,26 +2112,26 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FCA FIAT CHRYSLER</t>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FCA FIAT CHRYSLER</t>
+          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2141,26 +2141,26 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FD DO BRASIL</t>
+          <t>FITCH RATINGS BRASIL LTDA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FD DO BRASIL</t>
+          <t>FITCH RATINGS BRASIL LTDA</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2170,23 +2170,23 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FIAT AUTO GOIANA</t>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FIAT AUTO GOIANA</t>
+          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2199,26 +2199,26 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL PARTICIPACOES E S</t>
+          <t>FPT INDUSTRIAL BRASIL LTDA</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2228,26 +2228,26 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FITCH RATINGS BRASIL LTDA</t>
+          <t>FUNDAÇAO REVIVER REFUGIO VIDA VERDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FITCH RATINGS BRASIL LTDA</t>
+          <t>FUNDAÇAO REVIVER REFUGIO VIDA VERDA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2257,23 +2257,23 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+          <t>GAS NATURAL SPS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FLIR SYSTEMS BR CAMERAS INFRA</t>
+          <t>GAS NATURAL SPS</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2286,23 +2286,23 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+          <t>GENERAL MILLS BR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FPT INDUSTRIAL BRASIL LTDA</t>
+          <t>GENERAL MILLS BR</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2315,20 +2315,20 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FUNDAÇAO REVIVER REFUGIO VIDA VERDA</t>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FUNDAÇAO REVIVER REFUGIO VIDA VERDA</t>
+          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -2344,23 +2344,23 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GAS NATURAL SPS</t>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GAS NATURAL SPS</t>
+          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>561</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2373,23 +2373,23 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GENERAL MILLS BR</t>
+          <t>GNB GAS NATURAL BR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GENERAL MILLS BR</t>
+          <t>GNB GAS NATURAL BR</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2402,23 +2402,23 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+          <t>GSK CONSUMO ONZE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GLAXOSMITHKLINE BRASIL PRODUTOS P C</t>
+          <t>GSK CONSUMO ONZE</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2431,26 +2431,26 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+          <t>GSK EVENTOS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GLOBO COMUNICACAO E PARTICIPAC</t>
+          <t>GSK EVENTOS</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2460,23 +2460,23 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GNB GAS NATURAL BR</t>
+          <t>GUERBET IMAGEM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GNB GAS NATURAL BR</t>
+          <t>GUERBET IMAGEM</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2489,23 +2489,23 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GSK CONSUMO ONZE</t>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GSK CONSUMO ONZE</t>
+          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2518,26 +2518,26 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GSK EVENTOS</t>
+          <t>HALEON BRASIL DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GSK EVENTOS</t>
+          <t>HALEON BRASIL DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2547,23 +2547,23 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUERBET IMAGEM</t>
+          <t>HARMAN DA AMAZONIA IND ELET E PARTI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GUERBET IMAGEM</t>
+          <t>HARMAN DA AMAZONIA IND ELET E PARTI</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2576,23 +2576,23 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+          <t>HARMAN DA AMAZONIA INDUSTRIA ELETRO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HALEON BRASIL DISTRIBUIDORA LT</t>
+          <t>HARMAN DA AMAZONIA INDUSTRIA ELETRO</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2605,26 +2605,26 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HALEON BRASIL DISTRIBUIDORA LTDA</t>
+          <t>HENKEL EMPLOYE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HALEON BRASIL DISTRIBUIDORA LTDA</t>
+          <t>HENKEL EMPLOYE</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HARMAN DA AMAZONIA IND ELET E PARTI</t>
+          <t>HITACHI ASTEMO CAMPINAS LTDA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HARMAN DA AMAZONIA IND ELET E PARTI</t>
+          <t>HITACHI ASTEMO CAMPINAS LTDA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2663,23 +2663,23 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HARMAN DA AMAZONIA INDUSTRIA ELETRO</t>
+          <t>HITACHI ENERGY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HARMAN DA AMAZONIA INDUSTRIA ELETRO</t>
+          <t>HITACHI ENERGY</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2692,26 +2692,26 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HENKEL EMPLOYE</t>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HENKEL EMPLOYE</t>
+          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E79" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2721,23 +2721,23 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HITACHI ASTEMO CAMPINAS LTDA</t>
+          <t>HONDA AUTOMOVEIS DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HITACHI ASTEMO CAMPINAS LTDA</t>
+          <t>HONDA AUTOMOVEIS DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2750,23 +2750,23 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HITACHI ENERGY</t>
+          <t>HONDA SERVICOS LTDA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HITACHI ENERGY</t>
+          <t>HONDA SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2779,23 +2779,23 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HITACHI VANTARA ADMINISTRACAO DE DA</t>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2808,23 +2808,23 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HONDA AUTOMOVEIS DO BRASIL LTDA</t>
+          <t>HUSQVARNA BR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HONDA AUTOMOVEIS DO BRASIL LTDA</t>
+          <t>HUSQVARNA BR</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2837,20 +2837,20 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HONDA SERVICOS LTDA</t>
+          <t>IDV BRASIL LTDA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HONDA SERVICOS LTDA</t>
+          <t>IDV BRASIL LTDA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
         <v>13</v>
@@ -2866,23 +2866,23 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+          <t>INSTITUTO EDP/EBTA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+          <t>INSTITUTO EDP/EBTA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2895,23 +2895,23 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HUSQVARNA BR</t>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HUSQVARNA BR</t>
+          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2924,23 +2924,23 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IDV BRASIL LTDA</t>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IDV BRASIL LTDA</t>
+          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2953,26 +2953,26 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>INSTITUTO EDP/EBTA</t>
+          <t>LEO BURNETT NEO/EBTA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>INSTITUTO EDP/EBTA</t>
+          <t>LEO BURNETT NEO/EBTA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2982,23 +2982,23 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+          <t>MCCANN ERICKSON</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JRC DO BRASIL EMPREENDIMENTOS ELETR</t>
+          <t>MCCANN ERICKSON</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3011,26 +3011,26 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+          <t>MCKINSEY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LENOVO TECNOLOGIA (BRASIL) LIMITADA</t>
+          <t>MCKINSEY</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3040,26 +3040,26 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LEO BURNETT NEO/EBTA</t>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LEO BURNETT NEO/EBTA</t>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3069,23 +3069,23 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MCCANN ERICKSON</t>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MCCANN ERICKSON</t>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3098,26 +3098,26 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MCKINSEY</t>
+          <t>MICROSOFT 272945 BRASIL LTDA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MCKINSEY</t>
+          <t>MICROSOFT 272945 BRASIL LTDA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3127,23 +3127,23 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+          <t>MICROSOFT DO BRASIL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+          <t>MICROSOFT DO BRASIL</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3156,26 +3156,26 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+          <t>MINASMAQUINAS JF LTDA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+          <t>MINASMAQUINAS JF LTDA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MICROSOFT 272945 BRASIL LTDA</t>
+          <t>MINASMAQUINAS SA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MICROSOFT 272945 BRASIL LTDA</t>
+          <t>MINASMAQUINAS SA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3214,26 +3214,26 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MICROSOFT DO BRASIL</t>
+          <t>MORGAN STANLEY CTVM S A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MICROSOFT DO BRASIL</t>
+          <t>MORGAN STANLEY CTVM S A</t>
         </is>
       </c>
       <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
         <v>8</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3243,26 +3243,26 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MINASMAQUINAS JF LTDA</t>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MINASMAQUINAS JF LTDA</t>
+          <t>MOTO HONDA DA AMAZONIA LTDA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3272,26 +3272,26 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MINASMAQUINAS SA</t>
+          <t>MOTOROLA MOBIL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MINASMAQUINAS SA</t>
+          <t>MOTOROLA MOBIL</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3301,26 +3301,26 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MORGAN STANLEY CTVM S A</t>
+          <t>MUNDIAL DISTRIBUIDO/EBTA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MORGAN STANLEY CTVM S A</t>
+          <t>MUNDIAL DISTRIBUIDO/EBTA</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3330,23 +3330,23 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+          <t>MUNDIAL SA/EBTA-20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MOTO HONDA DA AMAZONIA LTDA</t>
+          <t>MUNDIAL SA/EBTA-20</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3359,26 +3359,26 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MOTOROLA MOBIL</t>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MOTOROLA MOBIL</t>
+          <t>MUNDIAL SA/EBTA/EBTA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3388,26 +3388,26 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MUNDIAL DISTRIBUIDO/EBTA</t>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MUNDIAL DISTRIBUIDO/EBTA</t>
+          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3417,23 +3417,23 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MUNDIAL SA/EBTA-20</t>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MUNDIAL SA/EBTA-20</t>
+          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -3446,26 +3446,26 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MUNDIAL SA/EBTA/EBTA</t>
+          <t>OMPI DO BRASIL INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MUNDIAL SA/EBTA/EBTA</t>
+          <t>OMPI DO BRASIL INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3475,23 +3475,23 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+          <t>ON HIGHWAY BRASIL LTDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NBA BRASIL BASKETBALL EMPREENDIMENT</t>
+          <t>ON HIGHWAY BRASIL LTDA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -3504,23 +3504,23 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NOURYON PULP AND PERFORMANCE INDUST</t>
+          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E107" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3533,23 +3533,23 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OMPI DO BRASIL INDUSTRIA E COMERCIO</t>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OMPI DO BRASIL INDUSTRIA E COMERCIO</t>
+          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -3562,23 +3562,23 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ON HIGHWAY BRASIL LTDA</t>
+          <t>PRATIL/EBTA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ON HIGHWAY BRASIL LTDA</t>
+          <t>PRATIL/EBTA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3591,23 +3591,23 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ONESUBSEA DO BRASIL SERVICOS SUBMAR</t>
+          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -3620,23 +3620,23 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PIEMONTE HOLDING DE PARTICIPACOES S</t>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3649,26 +3649,26 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PRATIL/EBTA</t>
+          <t>REGIONAL BH</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PRATIL/EBTA</t>
+          <t>REGIONAL BH</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
         <v>2</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3678,26 +3678,26 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+          <t>RENAULT DO BRASIL S A</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PROSEGUR BRASIL SA TRANSP DE VAL E</t>
+          <t>RENAULT DO BRASIL S A</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3707,23 +3707,23 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+          <t>RETARGETLY BRASIL SISTEMAS LTDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+          <t>RETARGETLY BRASIL SISTEMAS LTDA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -3736,26 +3736,26 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>REGIONAL BH</t>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>REGIONAL BH</t>
+          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E115" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="F115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3765,26 +3765,26 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RENAULT DO BRASIL S A</t>
+          <t>SDOISPUBLICOM EBTA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RENAULT DO BRASIL S A</t>
+          <t>SDOISPUBLICOM EBTA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E116" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3794,23 +3794,23 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RETARGETLY BRASIL SISTEMAS LTDA</t>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RETARGETLY BRASIL SISTEMAS LTDA</t>
+          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -3823,23 +3823,23 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SCHLUMBERGER SERVICOS DE PETROLEO L</t>
+          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3852,26 +3852,26 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SDOISPUBLICOM EBTA</t>
+          <t>SERRA GRANDE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SDOISPUBLICOM EBTA</t>
+          <t>SERRA GRANDE</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3881,23 +3881,23 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+          <t>SIDEL DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SEGURPRO TEC EM SIST SEG ELET INCEN</t>
+          <t>SIDEL DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3910,20 +3910,20 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+          <t>SITA INC DO BRASIL /EBTA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SEGURPRO VIGILANCIA PATRIMONIAL SA</t>
+          <t>SITA INC DO BRASIL /EBTA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E121" t="n">
         <v>6</v>
@@ -3939,23 +3939,23 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SERRA GRANDE</t>
+          <t>TALENT MARCEL/EBTA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SERRA GRANDE</t>
+          <t>TALENT MARCEL/EBTA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3968,23 +3968,23 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SIDEL DO BRASIL LTDA</t>
+          <t>TBB PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SIDEL DO BRASIL LTDA</t>
+          <t>TBB PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3997,23 +3997,23 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SITA INC DO BRASIL /EBTA</t>
+          <t>TEKSID IRON DO BRASIL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SITA INC DO BRASIL /EBTA</t>
+          <t>TEKSID IRON DO BRASIL</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -4026,26 +4026,26 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TALENT MARCEL/EBTA</t>
+          <t>THE BOSTON CONSU</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TALENT MARCEL/EBTA</t>
+          <t>THE BOSTON CONSU</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4055,26 +4055,26 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TBB PUBLICIDADE LTDA</t>
+          <t>TOWERS WATSON</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TBB PUBLICIDADE LTDA</t>
+          <t>TOWERS WATSON</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4084,23 +4084,23 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TEKSID IRON DO BRASIL</t>
+          <t>TRACTEBEL ADMINISTRACAO E GERENCIAM</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TEKSID IRON DO BRASIL</t>
+          <t>TRACTEBEL ADMINISTRACAO E GERENCIAM</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4113,26 +4113,26 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>THE BOSTON CONSU</t>
+          <t>TRACTEBEL ENGI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>THE BOSTON CONSU</t>
+          <t>TRACTEBEL ENGI</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4142,26 +4142,26 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TOWERS WATSON</t>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TOWERS WATSON</t>
+          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4171,23 +4171,23 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TRACTEBEL ADMINISTRACAO E GERENCIAM</t>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TRACTEBEL ADMINISTRACAO E GERENCIAM</t>
+          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4200,23 +4200,23 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TRACTEBEL ENGI</t>
+          <t>UBS BRASIL ADMINISTRADORA DE VALORE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TRACTEBEL ENGI</t>
+          <t>UBS BRASIL ADMINISTRADORA DE VALORE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -4229,23 +4229,23 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TRANSPORTADORA ASSOCIADA DE GAS</t>
+          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E132" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4258,23 +4258,23 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TRANSUNION BRASIL SISTEMAS EM INFOR</t>
+          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4287,23 +4287,23 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>UBS BRASIL ADMINISTRADORA DE VALORE</t>
+          <t>UBS BRASIL SERVICOS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>UBS BRASIL ADMINISTRADORA DE VALORE</t>
+          <t>UBS BRASIL SERVICOS</t>
         </is>
       </c>
       <c r="D134" t="n">
+        <v>6</v>
+      </c>
+      <c r="E134" t="n">
         <v>2</v>
-      </c>
-      <c r="E134" t="n">
-        <v>1</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -4316,26 +4316,26 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UBS BRASIL CORRETORA DE CAMBIO, TIT</t>
+          <t>VALLOUREC S TUBULAR/EBTA</t>
         </is>
       </c>
       <c r="D135" t="n">
+        <v>9</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
         <v>7</v>
-      </c>
-      <c r="E135" t="n">
-        <v>3</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4345,23 +4345,23 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>UBS BRASIL CORRETORA DE VALORES SA</t>
+          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -4374,23 +4374,23 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>UBS BRASIL SERVICOS</t>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UBS BRASIL SERVICOS</t>
+          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4403,26 +4403,26 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VALLOUREC S TUBULAR/EBTA</t>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VALLOUREC S TUBULAR/EBTA</t>
+          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4432,20 +4432,20 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+          <t>WARNER BROS SOUTH INC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VALLOUREC SOLUCOES TUBULARES DO BRA</t>
+          <t>WARNER BROS SOUTH INC</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E139" t="n">
         <v>5</v>
@@ -4461,26 +4461,26 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+          <t>WILLIS AFFINITY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VALLOUREC TUBOS INDUSTRIAIS LTDA  3</t>
+          <t>WILLIS AFFINITY</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4490,23 +4490,23 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+          <t>WILLIS CORRETO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>VERISK DO BRASIL INFORMACOES ANALIT</t>
+          <t>WILLIS CORRETO</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -4519,23 +4519,23 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WARNER BROS SOUTH INC</t>
+          <t>WILLIS RESSEGUROS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>WARNER BROS SOUTH INC</t>
+          <t>WILLIS RESSEGUROS</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -4548,115 +4548,28 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46154.43059595256</v>
+        <v>46154.52336809108</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WILLIS AFFINITY</t>
+          <t>WORLPAY DO BRASIL INSTITUICAO DE PA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>WILLIS AFFINITY</t>
+          <t>WORLPAY DO BRASIL INSTITUICAO DE PA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>46154.43059595256</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>WILLIS CORRETO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>WILLIS CORRETO</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>7</v>
-      </c>
-      <c r="E144" t="n">
-        <v>12</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>46154.43059595256</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>WILLIS RESSEGUROS</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>WILLIS RESSEGUROS</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>46154.43059595256</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>WORLPAY DO BRASIL INSTITUICAO DE PA</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>WORLPAY DO BRASIL INSTITUICAO DE PA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>4</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,6 +1278,822 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ANDROMEDA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>54</v>
+      </c>
+      <c r="E26" t="n">
+        <v>240</v>
+      </c>
+      <c r="F26" t="n">
+        <v>47</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>APOLLO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>496</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AQUILES</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ELETROPAULO 23/EBTA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>190</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>34</v>
+      </c>
+      <c r="E29" t="n">
+        <v>386</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" t="n">
+        <v>33</v>
+      </c>
+      <c r="F30" t="n">
+        <v>34</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ASTRA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>113</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AURORA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" t="n">
+        <v>185</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CENTAURUS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>82</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2238</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CORAL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>133</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7531</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>COSMOS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13</v>
+      </c>
+      <c r="E35" t="n">
+        <v>190</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>60</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2827</v>
+      </c>
+      <c r="F36" t="n">
+        <v>32</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EVENTOS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>17</v>
+      </c>
+      <c r="E37" t="n">
+        <v>583</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DRIV BRASIL SOLUCOES AUTOMOTIVAS LT</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>304</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GENESIS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LAGUNA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NAUTILUS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>58</v>
+      </c>
+      <c r="E41" t="n">
+        <v>251</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OMEGA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HOWDEN SOUTH AMERICA VENTILADO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>17</v>
+      </c>
+      <c r="E42" t="n">
+        <v>74</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ORBIS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MERCOSUL LINE NAVEGACAO E LOGISTICA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>17</v>
+      </c>
+      <c r="E43" t="n">
+        <v>936</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORION </t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>170</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PROMETHEUS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MUNDIAL SA/EBTA-20</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>14</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PULSE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>11</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SIRIUS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GENERAL MILLS BR</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>61</v>
+      </c>
+      <c r="E47" t="n">
+        <v>116</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SUPERNOVA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>643</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>73</v>
+      </c>
+      <c r="E49" t="n">
+        <v>165</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -1296,7 +1296,7 @@
         <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F26" t="n">
         <v>47</v>
@@ -1330,7 +1330,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>496</v>
+        <v>600</v>
       </c>
       <c r="F27" t="n">
         <v>26</v>
@@ -1364,7 +1364,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
@@ -1398,7 +1398,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n">
         <v>34</v>
@@ -1466,7 +1466,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>82</v>
       </c>
       <c r="E33" t="n">
-        <v>2238</v>
+        <v>2674</v>
       </c>
       <c r="F33" t="n">
         <v>35</v>
@@ -1568,7 +1568,7 @@
         <v>133</v>
       </c>
       <c r="E34" t="n">
-        <v>7531</v>
+        <v>9005</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="F35" t="n">
         <v>12</v>
@@ -1636,7 +1636,7 @@
         <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>2827</v>
+        <v>3373</v>
       </c>
       <c r="F36" t="n">
         <v>32</v>
@@ -1670,7 +1670,7 @@
         <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>583</v>
+        <v>705</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>1266</v>
+        <v>1502</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>58</v>
       </c>
       <c r="E41" t="n">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
         <v>17</v>
       </c>
       <c r="E42" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
@@ -1874,7 +1874,7 @@
         <v>17</v>
       </c>
       <c r="E43" t="n">
-        <v>936</v>
+        <v>1096</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -1908,7 +1908,7 @@
         <v>170</v>
       </c>
       <c r="E44" t="n">
-        <v>1942</v>
+        <v>2266</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -1942,7 +1942,7 @@
         <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>61</v>
       </c>
       <c r="E47" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F47" t="n">
         <v>6</v>
@@ -2044,7 +2044,7 @@
         <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>643</v>
+        <v>765</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -2078,7 +2078,7 @@
         <v>73</v>
       </c>
       <c r="E49" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2094,6 +2094,822 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ANDROMEDA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>54</v>
+      </c>
+      <c r="E50" t="n">
+        <v>264</v>
+      </c>
+      <c r="F50" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>APOLLO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" t="n">
+        <v>572</v>
+      </c>
+      <c r="F51" t="n">
+        <v>26</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AQUILES</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>198</v>
+      </c>
+      <c r="F52" t="n">
+        <v>14</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>34</v>
+      </c>
+      <c r="E53" t="n">
+        <v>330</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12</v>
+      </c>
+      <c r="E54" t="n">
+        <v>33</v>
+      </c>
+      <c r="F54" t="n">
+        <v>34</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ASTRA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>121</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AURORA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14</v>
+      </c>
+      <c r="E56" t="n">
+        <v>209</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CENTAURUS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>82</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F57" t="n">
+        <v>35</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CORAL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>133</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8107</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>COSMOS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13</v>
+      </c>
+      <c r="E59" t="n">
+        <v>154</v>
+      </c>
+      <c r="F59" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3003</v>
+      </c>
+      <c r="F60" t="n">
+        <v>32</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EVENTOS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>17</v>
+      </c>
+      <c r="E61" t="n">
+        <v>671</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>352</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GENESIS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>16</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1298</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LAGUNA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>55</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NAUTILUS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
+        <v>319</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OMEGA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>17</v>
+      </c>
+      <c r="E66" t="n">
+        <v>66</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ORBIS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>17</v>
+      </c>
+      <c r="E67" t="n">
+        <v>880</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORION </t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>REGIONAL BH</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>170</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1782</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PROMETHEUS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" t="n">
+        <v>22</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PULSE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SIRIUS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>61</v>
+      </c>
+      <c r="E71" t="n">
+        <v>132</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SUPERNOVA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="n">
+        <v>671</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>72</v>
+      </c>
+      <c r="E73" t="n">
+        <v>220</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2910,6 +2910,822 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ANDROMEDA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>54</v>
+      </c>
+      <c r="E74" t="n">
+        <v>144</v>
+      </c>
+      <c r="F74" t="n">
+        <v>47</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>APOLLO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>312</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AQUILES</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>108</v>
+      </c>
+      <c r="F76" t="n">
+        <v>14</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>34</v>
+      </c>
+      <c r="E77" t="n">
+        <v>180</v>
+      </c>
+      <c r="F77" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12</v>
+      </c>
+      <c r="E78" t="n">
+        <v>18</v>
+      </c>
+      <c r="F78" t="n">
+        <v>34</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ASTRA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>6</v>
+      </c>
+      <c r="E79" t="n">
+        <v>66</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AURORA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>14</v>
+      </c>
+      <c r="E80" t="n">
+        <v>114</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CENTAURUS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>82</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F81" t="n">
+        <v>35</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CORAL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>133</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4422</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>COSMOS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13</v>
+      </c>
+      <c r="E83" t="n">
+        <v>84</v>
+      </c>
+      <c r="F83" t="n">
+        <v>12</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>58</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1638</v>
+      </c>
+      <c r="F84" t="n">
+        <v>34</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EVENTOS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>16</v>
+      </c>
+      <c r="E85" t="n">
+        <v>372</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
+        <v>192</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GENESIS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>16</v>
+      </c>
+      <c r="E87" t="n">
+        <v>708</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LAGUNA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>30</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NAUTILUS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>52</v>
+      </c>
+      <c r="E89" t="n">
+        <v>204</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OMEGA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>17</v>
+      </c>
+      <c r="E90" t="n">
+        <v>36</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ORBIS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>17</v>
+      </c>
+      <c r="E91" t="n">
+        <v>480</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORION </t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>REGIONAL BH</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>170</v>
+      </c>
+      <c r="E92" t="n">
+        <v>972</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PROMETHEUS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>9</v>
+      </c>
+      <c r="E93" t="n">
+        <v>12</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PULSE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SIRIUS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>60</v>
+      </c>
+      <c r="E95" t="n">
+        <v>78</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SUPERNOVA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>8</v>
+      </c>
+      <c r="E96" t="n">
+        <v>366</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>72</v>
+      </c>
+      <c r="E97" t="n">
+        <v>120</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,53 +429,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>data_execucao</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>celula</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome da Empresa</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>incorretos</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>corretos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ausencia_de_dados</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>status_email</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>usuario</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,7 +543,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,7 +577,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -599,7 +611,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -633,7 +645,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -667,7 +679,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +713,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -735,7 +747,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -769,7 +781,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -837,7 +849,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +883,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -905,7 +917,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -939,7 +951,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -973,7 +985,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,7 +1019,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1041,7 +1053,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1087,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1155,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1177,7 +1189,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1211,7 +1223,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1245,7 +1257,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1279,7 +1291,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1347,7 +1359,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1381,7 +1393,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1415,7 +1427,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1517,7 +1529,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1551,7 +1563,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1585,7 +1597,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1619,7 +1631,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1653,7 +1665,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1687,7 +1699,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1721,7 +1733,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1755,7 +1767,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1801,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1823,7 +1835,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1857,7 +1869,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1891,7 +1903,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1925,7 +1937,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1959,7 +1971,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1993,7 +2005,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2027,7 +2039,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2061,7 +2073,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,7 +2107,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2129,7 +2141,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2163,7 +2175,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2197,7 +2209,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2231,7 +2243,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2265,7 +2277,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2299,7 +2311,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2367,7 +2379,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2401,7 +2413,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2435,7 +2447,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2537,7 +2549,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2571,7 +2583,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2605,7 +2617,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2639,7 +2651,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2673,7 +2685,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2741,7 +2753,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2775,7 +2787,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2809,7 +2821,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2843,7 +2855,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2877,7 +2889,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2911,7 +2923,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2945,7 +2957,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2979,7 +2991,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3013,7 +3025,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3047,7 +3059,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3081,7 +3093,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3115,7 +3127,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3149,7 +3161,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3183,7 +3195,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3217,7 +3229,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3251,7 +3263,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3285,7 +3297,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3319,7 +3331,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3353,7 +3365,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3387,7 +3399,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3421,7 +3433,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3455,7 +3467,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3489,7 +3501,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3523,7 +3535,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3557,7 +3569,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3591,7 +3603,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -3625,7 +3637,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -3659,7 +3671,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -3693,7 +3705,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -3723,6 +3735,822 @@
       <c r="H97" t="inlineStr">
         <is>
           <t>nicolas.cavalcante</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ANDROMEDA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>54</v>
+      </c>
+      <c r="E98" t="n">
+        <v>144</v>
+      </c>
+      <c r="F98" t="n">
+        <v>47</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>APOLLO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>6</v>
+      </c>
+      <c r="E99" t="n">
+        <v>312</v>
+      </c>
+      <c r="F99" t="n">
+        <v>26</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AQUILES</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>108</v>
+      </c>
+      <c r="F100" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>34</v>
+      </c>
+      <c r="E101" t="n">
+        <v>180</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12</v>
+      </c>
+      <c r="E102" t="n">
+        <v>18</v>
+      </c>
+      <c r="F102" t="n">
+        <v>34</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ASTRA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" t="n">
+        <v>66</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AURORA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>14</v>
+      </c>
+      <c r="E104" t="n">
+        <v>114</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CENTAURUS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>82</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F105" t="n">
+        <v>35</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CORAL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>QLIKTECH BRASIL COM SOF LTDA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>133</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4422</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>COSMOS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>13</v>
+      </c>
+      <c r="E107" t="n">
+        <v>84</v>
+      </c>
+      <c r="F107" t="n">
+        <v>12</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>58</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1638</v>
+      </c>
+      <c r="F108" t="n">
+        <v>34</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EVENTOS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>16</v>
+      </c>
+      <c r="E109" t="n">
+        <v>372</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="n">
+        <v>192</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GENESIS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>16</v>
+      </c>
+      <c r="E111" t="n">
+        <v>708</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LAGUNA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>30</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NAUTILUS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>50</v>
+      </c>
+      <c r="E113" t="n">
+        <v>216</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OMEGA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>HENKEL EMPLOYE</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>17</v>
+      </c>
+      <c r="E114" t="n">
+        <v>36</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ORBIS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>17</v>
+      </c>
+      <c r="E115" t="n">
+        <v>480</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORION </t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>REGIONAL BH</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>170</v>
+      </c>
+      <c r="E116" t="n">
+        <v>972</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PROMETHEUS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>9</v>
+      </c>
+      <c r="E117" t="n">
+        <v>12</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PULSE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CNH INDUSTRIAL BRASIL</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" t="n">
+        <v>6</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SIRIUS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>59</v>
+      </c>
+      <c r="E119" t="n">
+        <v>78</v>
+      </c>
+      <c r="F119" t="n">
+        <v>7</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SUPERNOVA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+      <c r="E120" t="n">
+        <v>366</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>HITACHI ENERGY</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
+        <v>120</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
         </is>
       </c>
     </row>

--- a/logs/historico_execucao_detalhado.xlsx
+++ b/logs/historico_execucao_detalhado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,53 +417,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>data_execucao</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>celula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome da Empresa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>incorretos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>corretos</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ausencia_de_dados</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>status_email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>usuario</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,7 +531,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +565,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -611,7 +599,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,7 +633,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -679,7 +667,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -713,7 +701,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -747,7 +735,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -781,7 +769,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -849,7 +837,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -883,7 +871,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -917,7 +905,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +939,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -985,7 +973,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1019,7 +1007,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1053,7 +1041,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1087,7 +1075,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1155,7 +1143,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1189,7 +1177,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1223,7 +1211,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1257,7 +1245,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1279,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1325,7 +1313,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1359,7 +1347,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1393,7 +1381,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,7 +1415,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1461,7 +1449,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1483,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1529,7 +1517,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1551,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1597,7 +1585,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1631,7 +1619,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1665,7 +1653,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1699,7 +1687,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1733,7 +1721,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1767,7 +1755,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1801,7 +1789,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1835,7 +1823,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1869,7 +1857,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,7 +1891,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1937,7 +1925,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1971,7 +1959,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2005,7 +1993,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2039,7 +2027,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2073,7 +2061,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2107,7 +2095,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2141,7 +2129,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2175,7 +2163,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2209,7 +2197,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2243,7 +2231,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2277,7 +2265,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2311,7 +2299,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2345,7 +2333,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2379,7 +2367,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2413,7 +2401,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2447,7 +2435,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2515,7 +2503,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2549,7 +2537,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2583,7 +2571,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2617,7 +2605,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2651,7 +2639,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2685,7 +2673,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2753,7 +2741,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2787,7 +2775,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2821,7 +2809,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2855,7 +2843,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2889,7 +2877,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2923,7 +2911,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2957,7 +2945,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2991,7 +2979,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3025,7 +3013,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3059,7 +3047,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3093,7 +3081,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3127,7 +3115,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3161,7 +3149,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3195,7 +3183,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3229,7 +3217,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3263,7 +3251,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3297,7 +3285,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3331,7 +3319,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3365,7 +3353,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3399,7 +3387,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3433,7 +3421,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3501,7 +3489,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3535,7 +3523,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3569,7 +3557,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3603,7 +3591,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -3637,7 +3625,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -3671,7 +3659,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -3705,7 +3693,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -3739,469 +3727,441 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ATLAS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>ANDROMEDA</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>54</v>
-      </c>
-      <c r="E98" t="n">
-        <v>144</v>
-      </c>
-      <c r="F98" t="n">
+      <c r="D99" t="n">
+        <v>68</v>
+      </c>
+      <c r="E99" t="n">
+        <v>320</v>
+      </c>
+      <c r="F99" t="n">
         <v>47</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
+    <row r="100">
+      <c r="A100" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>APOLLO</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>CNH INDUSTRIAL BRASIL</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D100" t="n">
         <v>6</v>
       </c>
-      <c r="E99" t="n">
-        <v>312</v>
-      </c>
-      <c r="F99" t="n">
+      <c r="E100" t="n">
+        <v>676</v>
+      </c>
+      <c r="F100" t="n">
         <v>26</v>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
+    <row r="101">
+      <c r="A101" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>AQUILES</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>CNH INDUSTRIAL BRASIL</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D101" t="n">
         <v>3</v>
       </c>
-      <c r="E100" t="n">
-        <v>108</v>
-      </c>
-      <c r="F100" t="n">
+      <c r="E101" t="n">
+        <v>234</v>
+      </c>
+      <c r="F101" t="n">
         <v>14</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
+    <row r="102">
+      <c r="A102" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>ARES</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D102" t="n">
         <v>34</v>
       </c>
-      <c r="E101" t="n">
-        <v>180</v>
-      </c>
-      <c r="F101" t="n">
+      <c r="E102" t="n">
+        <v>390</v>
+      </c>
+      <c r="F102" t="n">
         <v>7</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
+    <row r="103">
+      <c r="A103" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>ARTEMIS</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D103" t="n">
         <v>12</v>
       </c>
-      <c r="E102" t="n">
-        <v>18</v>
-      </c>
-      <c r="F102" t="n">
+      <c r="E103" t="n">
+        <v>39</v>
+      </c>
+      <c r="F103" t="n">
         <v>34</v>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
+    <row r="104">
+      <c r="A104" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>ASTRA</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D104" t="n">
         <v>6</v>
       </c>
-      <c r="E103" t="n">
-        <v>66</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
+      <c r="E104" t="n">
+        <v>143</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ATLAS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>AURORA</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D106" t="n">
         <v>14</v>
       </c>
-      <c r="E104" t="n">
-        <v>114</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="E106" t="n">
+        <v>247</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
+    <row r="107">
+      <c r="A107" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>CENTAURUS</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D107" t="n">
         <v>82</v>
       </c>
-      <c r="E105" t="n">
-        <v>1308</v>
-      </c>
-      <c r="F105" t="n">
+      <c r="E107" t="n">
+        <v>2834</v>
+      </c>
+      <c r="F107" t="n">
         <v>35</v>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
+    <row r="108">
+      <c r="A108" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>CORAL</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>QLIKTECH BRASIL COM SOF LTDA</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D108" t="n">
         <v>133</v>
       </c>
-      <c r="E106" t="n">
-        <v>4422</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="E108" t="n">
+        <v>9581</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
+    <row r="109">
+      <c r="A109" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>COSMOS</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>MCCANN ERICKSON</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D109" t="n">
         <v>13</v>
       </c>
-      <c r="E107" t="n">
-        <v>84</v>
-      </c>
-      <c r="F107" t="n">
+      <c r="E109" t="n">
+        <v>182</v>
+      </c>
+      <c r="F109" t="n">
         <v>12</v>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
+    <row r="110">
+      <c r="A110" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>DISCOVERY</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D110" t="n">
         <v>58</v>
       </c>
-      <c r="E108" t="n">
-        <v>1638</v>
-      </c>
-      <c r="F108" t="n">
+      <c r="E110" t="n">
+        <v>3549</v>
+      </c>
+      <c r="F110" t="n">
         <v>34</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
+    <row r="111">
+      <c r="A111" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>EVENTOS</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>16</v>
-      </c>
-      <c r="E109" t="n">
-        <v>372</v>
-      </c>
-      <c r="F109" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>nathalia.santos</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10</v>
-      </c>
-      <c r="E110" t="n">
-        <v>192</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>nathalia.santos</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>GENESIS</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>MCCANN ERICKSON</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>16</v>
       </c>
       <c r="E111" t="n">
-        <v>708</v>
+        <v>806</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4215,340 +4175,408 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MEDIABRANDS PUBLICIDADE LTDA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="n">
+        <v>416</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GENESIS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MCCANN ERICKSON</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>16</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1534</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>nathalia.santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>LAGUNA</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>MCCANN ERICKSON</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D114" t="n">
         <v>2</v>
       </c>
-      <c r="E112" t="n">
-        <v>30</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="E114" t="n">
+        <v>65</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
+    <row r="115">
+      <c r="A115" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>NAUTILUS</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>HITACHI ENERGY</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>50</v>
-      </c>
-      <c r="E113" t="n">
-        <v>216</v>
-      </c>
-      <c r="F113" t="n">
+      <c r="D115" t="n">
+        <v>52</v>
+      </c>
+      <c r="E115" t="n">
+        <v>542</v>
+      </c>
+      <c r="F115" t="n">
         <v>1</v>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
+    <row r="116">
+      <c r="A116" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>OMEGA</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>HENKEL EMPLOYE</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D116" t="n">
         <v>17</v>
       </c>
-      <c r="E114" t="n">
-        <v>36</v>
-      </c>
-      <c r="F114" t="n">
+      <c r="E116" t="n">
+        <v>78</v>
+      </c>
+      <c r="F116" t="n">
         <v>8</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
+    <row r="117">
+      <c r="A117" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>ORBIS</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>MCCANN ERICKSON</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D117" t="n">
         <v>17</v>
       </c>
-      <c r="E115" t="n">
-        <v>480</v>
-      </c>
-      <c r="F115" t="n">
+      <c r="E117" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F117" t="n">
         <v>8</v>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
+    <row r="118">
+      <c r="A118" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t xml:space="preserve">ORION </t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>REGIONAL BH</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D118" t="n">
         <v>170</v>
       </c>
-      <c r="E116" t="n">
-        <v>972</v>
-      </c>
-      <c r="F116" t="n">
+      <c r="E118" t="n">
+        <v>2106</v>
+      </c>
+      <c r="F118" t="n">
         <v>3</v>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
+    <row r="119">
+      <c r="A119" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>PROMETHEUS</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>CNH INDUSTRIAL BRASIL</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="D119" t="n">
         <v>9</v>
       </c>
-      <c r="E117" t="n">
-        <v>12</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
+      <c r="E119" t="n">
+        <v>26</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
+    <row r="120">
+      <c r="A120" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>PULSE</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>CNH INDUSTRIAL BRASIL</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D120" t="n">
         <v>4</v>
       </c>
-      <c r="E118" t="n">
-        <v>6</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
+      <c r="E120" t="n">
+        <v>13</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
+    <row r="121">
+      <c r="A121" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>SIRIUS</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>HITACHI ENERGY</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>59</v>
-      </c>
-      <c r="E119" t="n">
-        <v>78</v>
-      </c>
-      <c r="F119" t="n">
+      <c r="D121" t="n">
+        <v>61</v>
+      </c>
+      <c r="E121" t="n">
+        <v>169</v>
+      </c>
+      <c r="F121" t="n">
         <v>7</v>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
+    <row r="122">
+      <c r="A122" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>SUPERNOVA</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>HITACHI ENERGY</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="D122" t="n">
         <v>8</v>
       </c>
-      <c r="E120" t="n">
-        <v>366</v>
-      </c>
-      <c r="F120" t="n">
+      <c r="E122" t="n">
+        <v>793</v>
+      </c>
+      <c r="F122" t="n">
         <v>1</v>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
+    <row r="123">
+      <c r="A123" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>VEGA</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>HITACHI ENERGY</t>
         </is>
       </c>
-      <c r="D121" t="n">
+      <c r="D123" t="n">
         <v>72</v>
       </c>
-      <c r="E121" t="n">
-        <v>120</v>
-      </c>
-      <c r="F121" t="n">
+      <c r="E123" t="n">
+        <v>260</v>
+      </c>
+      <c r="F123" t="n">
         <v>1</v>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
         <is>
           <t>nathalia.santos</t>
         </is>
